--- a/inputs/sales_volumes_last_month_test.xlsx
+++ b/inputs/sales_volumes_last_month_test.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/786a008dc9bd2781/Python/4. HT/0. T GLobal eSIM/T GLobal robopricing/inputs/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hrtelekom-my.sharepoint.com/personal/diego_deblock_t_ht_hr/Documents/Documents/Python/TT-Robopricing/inputs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{1DE9A8EF-5FF9-4D65-A67F-FB542CA3DE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4786305C-097C-4F0C-BAB7-387D242ADBF2}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{1DE9A8EF-5FF9-4D65-A67F-FB542CA3DE0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8710A017-EC1D-4A7B-AC8B-623D4471C7AD}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{E4303EF8-C524-4DA8-A50B-84EBBCDEE712}"/>
+    <workbookView xWindow="2985" yWindow="2985" windowWidth="34515" windowHeight="11775" xr2:uid="{E4303EF8-C524-4DA8-A50B-84EBBCDEE712}"/>
   </bookViews>
   <sheets>
     <sheet name="sales_volumes_last_month_test" sheetId="1" r:id="rId1"/>
@@ -929,12 +929,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15C7AAF4-FBB3-4BAB-84E2-EB8A6D9DA874}">
   <dimension ref="A1:G4"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="17" customWidth="1"/>
+    <col min="3" max="3" width="17.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -957,7 +957,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -980,7 +980,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -1003,7 +1003,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>13</v>
       </c>
